--- a/Bang_ke_hoach_chi_spa_100tr.xlsx
+++ b/Bang_ke_hoach_chi_spa_100tr.xlsx
@@ -5,10 +5,10 @@
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\LongHN5\P_SPA_TINHTOAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A954B35B-E276-4871-B7DC-36B38E1AA245}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EEF73A1-D382-4C4F-ACC0-BE2D0B4C1B95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="31">
   <si>
     <t>Tháng 1</t>
   </si>
@@ -105,25 +105,7 @@
     <t>Sau cưới</t>
   </si>
   <si>
-    <t>Column1</t>
-  </si>
-  <si>
-    <t>Sum</t>
-  </si>
-  <si>
-    <t>Average</t>
-  </si>
-  <si>
-    <t>Running Total</t>
-  </si>
-  <si>
-    <t>Count</t>
-  </si>
-  <si>
     <t>Học liệu trình+ bằng</t>
-  </si>
-  <si>
-    <t>Bù lỗ</t>
   </si>
   <si>
     <t>Tổng chi</t>
@@ -136,6 +118,12 @@
   </si>
   <si>
     <t>B. Tổng chi theo tháng</t>
+  </si>
+  <si>
+    <t>Khấu hao thiết bị</t>
+  </si>
+  <si>
+    <t>Sửa tiệm + loa</t>
   </si>
 </sst>
 </file>
@@ -392,7 +380,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>KeHoachChi!$M$1</c:f>
+              <c:f>KeHoachChi!$L$17</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -498,7 +486,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>KeHoachChi!$L$2:$L$7</c:f>
+              <c:f>KeHoachChi!$K$18:$K$23</c:f>
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
@@ -524,27 +512,27 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>KeHoachChi!$M$2:$M$7</c:f>
+              <c:f>KeHoachChi!$L$18:$L$23</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>108700000</c:v>
+                  <c:v>119200000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>12700000</c:v>
+                  <c:v>13200000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>19700000</c:v>
+                  <c:v>20200000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>19700000</c:v>
+                  <c:v>20200000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>19700000</c:v>
+                  <c:v>20200000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>15700000</c:v>
+                  <c:v>16200000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -560,7 +548,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>KeHoachChi!$N$1</c:f>
+              <c:f>KeHoachChi!$M$17</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -666,7 +654,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>KeHoachChi!$L$2:$L$7</c:f>
+              <c:f>KeHoachChi!$K$18:$K$23</c:f>
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
@@ -692,27 +680,27 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>KeHoachChi!$N$2:$N$7</c:f>
+              <c:f>KeHoachChi!$M$18:$M$23</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>3748275.8620689656</c:v>
+                  <c:v>4110344.8275862071</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>437931.03448275861</c:v>
+                  <c:v>455172.41379310342</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>679310.3448275862</c:v>
+                  <c:v>696551.72413793101</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>679310.3448275862</c:v>
+                  <c:v>696551.72413793101</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>679310.3448275862</c:v>
+                  <c:v>696551.72413793101</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>541379.31034482759</c:v>
+                  <c:v>558620.68965517241</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -972,6 +960,11 @@
               </a:effectLst>
               <a:sp3d/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-6B1E-4860-AE24-EEA07D32EF3A}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -992,6 +985,11 @@
               </a:effectLst>
               <a:sp3d/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-6B1E-4860-AE24-EEA07D32EF3A}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
@@ -1012,6 +1010,11 @@
               </a:effectLst>
               <a:sp3d/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-6B1E-4860-AE24-EEA07D32EF3A}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="3"/>
@@ -1032,6 +1035,11 @@
               </a:effectLst>
               <a:sp3d/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-6B1E-4860-AE24-EEA07D32EF3A}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="4"/>
@@ -1052,6 +1060,11 @@
               </a:effectLst>
               <a:sp3d/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000009-6B1E-4860-AE24-EEA07D32EF3A}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="5"/>
@@ -1072,6 +1085,11 @@
               </a:effectLst>
               <a:sp3d/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000B-6B1E-4860-AE24-EEA07D32EF3A}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="6"/>
@@ -1094,6 +1112,11 @@
               </a:effectLst>
               <a:sp3d/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000D-6B1E-4860-AE24-EEA07D32EF3A}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="7"/>
@@ -1116,6 +1139,11 @@
               </a:effectLst>
               <a:sp3d/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000F-6B1E-4860-AE24-EEA07D32EF3A}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="8"/>
@@ -1138,6 +1166,11 @@
               </a:effectLst>
               <a:sp3d/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000011-6B1E-4860-AE24-EEA07D32EF3A}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="9"/>
@@ -1160,6 +1193,11 @@
               </a:effectLst>
               <a:sp3d/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000013-6B1E-4860-AE24-EEA07D32EF3A}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="10"/>
@@ -1168,6 +1206,61 @@
               <a:solidFill>
                 <a:schemeClr val="accent5">
                   <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="20000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:sp3d/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000015-6B1E-4860-AE24-EEA07D32EF3A}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="11"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="20000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:sp3d/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000017-7929-4866-AEE6-266650D002A1}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="12"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="80000"/>
+                  <a:lumOff val="20000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:ln>
@@ -1256,9 +1349,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>KeHoachChi!$B$2:$B$12</c:f>
+              <c:f>KeHoachChi!$B$2:$B$14</c:f>
               <c:strCache>
-                <c:ptCount val="11"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>Mặt bằng</c:v>
                 </c:pt>
@@ -1275,32 +1368,35 @@
                   <c:v>Ăn uống sinh hoạt</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>Khấu hao thiết bị</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>Sang mặt bằng</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>Học liệu trình+ bằng</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>Sản phẩm</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>Đồng phục</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
                   <c:v>Máy móc dụng cụ</c:v>
                 </c:pt>
-                <c:pt idx="10">
-                  <c:v>Bù lỗ</c:v>
+                <c:pt idx="11">
+                  <c:v>Sửa tiệm + loa</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>KeHoachChi!$E$2:$E$12</c:f>
+              <c:f>KeHoachChi!$E$2:$E$14</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
                   <c:v>7000000</c:v>
                 </c:pt>
@@ -1315,6 +1411,9 @@
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>5000000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>500000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2673,13 +2772,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>127152</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>29935</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>498929</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>98273</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -2709,13 +2808,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>65012</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>19351</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>811893</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>41123</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -2745,8 +2844,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A1BCB148-CB9E-49F0-AB94-0F8783D87BF7}" name="Table1" displayName="Table1" ref="B1:J12" totalsRowShown="0" headerRowDxfId="9">
-  <autoFilter ref="B1:J12" xr:uid="{A1BCB148-CB9E-49F0-AB94-0F8783D87BF7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A1BCB148-CB9E-49F0-AB94-0F8783D87BF7}" name="Table1" displayName="Table1" ref="B1:J14" totalsRowShown="0" headerRowDxfId="9">
+  <autoFilter ref="B1:J14" xr:uid="{A1BCB148-CB9E-49F0-AB94-0F8783D87BF7}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{FABC7689-FBD7-4C51-AECB-719A63BFAB25}" name="Hạng mục chi"/>
     <tableColumn id="2" xr3:uid="{F67B38AB-C8FD-4E24-B51F-51EF7C465498}" name="Tháng 1" dataDxfId="8"/>
@@ -2763,8 +2862,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{8C67B107-8B4B-4E50-B8FB-D63C28DDDD6B}" name="Table2" displayName="Table2" ref="L1:N7" totalsRowShown="0">
-  <autoFilter ref="L1:N7" xr:uid="{8C67B107-8B4B-4E50-B8FB-D63C28DDDD6B}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{8C67B107-8B4B-4E50-B8FB-D63C28DDDD6B}" name="Table2" displayName="Table2" ref="K17:M23" totalsRowShown="0">
+  <autoFilter ref="K17:M23" xr:uid="{8C67B107-8B4B-4E50-B8FB-D63C28DDDD6B}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{FE865CD0-F680-430E-8813-BF45636D1370}" name="Tháng"/>
     <tableColumn id="2" xr3:uid="{A2C1C32D-FD26-4714-AAFF-2D1A0615AA98}" name="Tổng chi" dataDxfId="1"/>
@@ -3061,7 +3160,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N23"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="24.7265625" customWidth="1"/>
@@ -3071,11 +3170,12 @@
     <col min="5" max="5" width="12.36328125" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="9" width="12.36328125" style="1" customWidth="1"/>
     <col min="10" max="10" width="9.08984375" customWidth="1"/>
+    <col min="12" max="12" width="11.81640625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="14.54296875" customWidth="1"/>
     <col min="14" max="14" width="21.54296875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B1" t="s">
         <v>13</v>
       </c>
@@ -3103,17 +3203,8 @@
       <c r="J1" t="s">
         <v>3</v>
       </c>
-      <c r="L1" t="s">
-        <v>22</v>
-      </c>
-      <c r="M1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>32</v>
-      </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>18</v>
       </c>
@@ -3142,19 +3233,8 @@
       <c r="J2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="L2" t="s">
-        <v>0</v>
-      </c>
-      <c r="M2" s="3">
-        <f>SUM(C:C)</f>
-        <v>108700000</v>
-      </c>
-      <c r="N2" s="5">
-        <f>Table2[[#This Row],[Tổng chi]]/29</f>
-        <v>3748275.8620689656</v>
-      </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" s="2"/>
       <c r="B3" s="6" t="s">
         <v>12</v>
@@ -3181,19 +3261,8 @@
         <v>1000000</v>
       </c>
       <c r="J3" s="6"/>
-      <c r="L3" t="s">
-        <v>1</v>
-      </c>
-      <c r="M3" s="3">
-        <f>SUM(D:D)</f>
-        <v>12700000</v>
-      </c>
-      <c r="N3" s="5">
-        <f>Table2[[#This Row],[Tổng chi]]/29</f>
-        <v>437931.03448275861</v>
-      </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" s="2"/>
       <c r="B4" s="6" t="s">
         <v>10</v>
@@ -3216,19 +3285,8 @@
       <c r="H4" s="8"/>
       <c r="I4" s="8"/>
       <c r="J4" s="6"/>
-      <c r="L4" t="s">
-        <v>2</v>
-      </c>
-      <c r="M4" s="3">
-        <f>SUM(E:E)</f>
-        <v>19700000</v>
-      </c>
-      <c r="N4" s="5">
-        <f>Table2[[#This Row],[Tổng chi]]/29</f>
-        <v>679310.3448275862</v>
-      </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="2"/>
       <c r="B5" s="6" t="s">
         <v>11</v>
@@ -3255,19 +3313,8 @@
         <v>2700000</v>
       </c>
       <c r="J5" s="6"/>
-      <c r="L5" t="s">
-        <v>15</v>
-      </c>
-      <c r="M5" s="3">
-        <f>SUM(F:F)</f>
-        <v>19700000</v>
-      </c>
-      <c r="N5" s="5">
-        <f>Table2[[#This Row],[Tổng chi]]/29</f>
-        <v>679310.3448275862</v>
-      </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="2"/>
       <c r="B6" s="6" t="s">
         <v>14</v>
@@ -3294,54 +3341,44 @@
         <v>5000000</v>
       </c>
       <c r="J6" s="6"/>
-      <c r="L6" t="s">
-        <v>16</v>
-      </c>
-      <c r="M6" s="3">
-        <f>SUM(G:G)</f>
-        <v>19700000</v>
-      </c>
-      <c r="N6" s="5">
-        <f>Table2[[#This Row],[Tổng chi]]/29</f>
-        <v>679310.3448275862</v>
-      </c>
     </row>
-    <row r="7" spans="1:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="9" t="s">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A7" s="2"/>
+      <c r="B7" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="7">
+        <v>500000</v>
+      </c>
+      <c r="D7" s="7">
+        <v>500000</v>
+      </c>
+      <c r="E7" s="7">
+        <v>500000</v>
+      </c>
+      <c r="F7" s="7">
+        <v>500000</v>
+      </c>
+      <c r="G7" s="7">
+        <v>500000</v>
+      </c>
+      <c r="H7" s="7">
+        <v>500000</v>
+      </c>
+      <c r="I7" s="7">
+        <v>500000</v>
+      </c>
+      <c r="J7" s="6"/>
+    </row>
+    <row r="8" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B8" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="11">
+      <c r="C8" s="11">
         <v>40000000</v>
-      </c>
-      <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="11"/>
-      <c r="J7" s="10"/>
-      <c r="L7" t="s">
-        <v>23</v>
-      </c>
-      <c r="M7" s="3">
-        <f>SUM(H:H)</f>
-        <v>15700000</v>
-      </c>
-      <c r="N7" s="5">
-        <f>Table2[[#This Row],[Tổng chi]]/29</f>
-        <v>541379.31034482759</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A8" s="9"/>
-      <c r="B8" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" s="11">
-        <v>20000000</v>
       </c>
       <c r="D8" s="11"/>
       <c r="E8" s="11"/>
@@ -3351,13 +3388,13 @@
       <c r="I8" s="11"/>
       <c r="J8" s="10"/>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" s="9"/>
       <c r="B9" s="10" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="C9" s="11">
-        <v>15000000</v>
+        <v>20000000</v>
       </c>
       <c r="D9" s="11"/>
       <c r="E9" s="11"/>
@@ -3365,17 +3402,15 @@
       <c r="G9" s="11"/>
       <c r="H9" s="11"/>
       <c r="I9" s="11"/>
-      <c r="J9" s="10" t="s">
-        <v>8</v>
-      </c>
+      <c r="J9" s="10"/>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" s="9"/>
       <c r="B10" s="10" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="C10" s="11">
-        <v>2000000</v>
+        <v>15000000</v>
       </c>
       <c r="D10" s="11"/>
       <c r="E10" s="11"/>
@@ -3383,15 +3418,17 @@
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
-      <c r="J10" s="10"/>
+      <c r="J10" s="10" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" s="9"/>
       <c r="B11" s="10" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C11" s="11">
-        <v>5000000</v>
+        <v>2000000</v>
       </c>
       <c r="D11" s="11"/>
       <c r="E11" s="11"/>
@@ -3401,12 +3438,14 @@
       <c r="I11" s="11"/>
       <c r="J11" s="10"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A12" s="10"/>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A12" s="9"/>
       <c r="B12" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" s="11"/>
+        <v>9</v>
+      </c>
+      <c r="C12" s="11">
+        <v>5000000</v>
+      </c>
       <c r="D12" s="11"/>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
@@ -3415,18 +3454,123 @@
       <c r="I12" s="11"/>
       <c r="J12" s="10"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A14" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>34</v>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A13" s="9"/>
+      <c r="B13" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="11">
+        <v>10000000</v>
+      </c>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="10"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A15" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17" spans="11:13" x14ac:dyDescent="0.35">
+      <c r="K17" t="s">
+        <v>22</v>
+      </c>
+      <c r="L17" t="s">
+        <v>25</v>
+      </c>
+      <c r="M17" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" spans="11:13" x14ac:dyDescent="0.35">
+      <c r="K18" t="s">
+        <v>0</v>
+      </c>
+      <c r="L18" s="3">
+        <f>SUM(C:C)</f>
+        <v>119200000</v>
+      </c>
+      <c r="M18" s="5">
+        <f>Table2[[#This Row],[Tổng chi]]/29</f>
+        <v>4110344.8275862071</v>
+      </c>
+    </row>
+    <row r="19" spans="11:13" x14ac:dyDescent="0.35">
+      <c r="K19" t="s">
+        <v>1</v>
+      </c>
+      <c r="L19" s="3">
+        <f>SUM(D:D)</f>
+        <v>13200000</v>
+      </c>
+      <c r="M19" s="5">
+        <f>Table2[[#This Row],[Tổng chi]]/29</f>
+        <v>455172.41379310342</v>
+      </c>
+    </row>
+    <row r="20" spans="11:13" x14ac:dyDescent="0.35">
+      <c r="K20" t="s">
+        <v>2</v>
+      </c>
+      <c r="L20" s="3">
+        <f>SUM(E:E)</f>
+        <v>20200000</v>
+      </c>
+      <c r="M20" s="5">
+        <f>Table2[[#This Row],[Tổng chi]]/29</f>
+        <v>696551.72413793101</v>
+      </c>
+    </row>
+    <row r="21" spans="11:13" x14ac:dyDescent="0.35">
+      <c r="K21" t="s">
+        <v>15</v>
+      </c>
+      <c r="L21" s="3">
+        <f>SUM(F:F)</f>
+        <v>20200000</v>
+      </c>
+      <c r="M21" s="5">
+        <f>Table2[[#This Row],[Tổng chi]]/29</f>
+        <v>696551.72413793101</v>
+      </c>
+    </row>
+    <row r="22" spans="11:13" x14ac:dyDescent="0.35">
+      <c r="K22" t="s">
+        <v>16</v>
+      </c>
+      <c r="L22" s="3">
+        <f>SUM(G:G)</f>
+        <v>20200000</v>
+      </c>
+      <c r="M22" s="5">
+        <f>Table2[[#This Row],[Tổng chi]]/29</f>
+        <v>696551.72413793101</v>
+      </c>
+    </row>
+    <row r="23" spans="11:13" x14ac:dyDescent="0.35">
+      <c r="K23" t="s">
+        <v>23</v>
+      </c>
+      <c r="L23" s="3">
+        <f>SUM(H:H)</f>
+        <v>16200000</v>
+      </c>
+      <c r="M23" s="5">
+        <f>Table2[[#This Row],[Tổng chi]]/29</f>
+        <v>558620.68965517241</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="M2:M7">
-    <cfRule type="dataBar" priority="3">
+  <conditionalFormatting sqref="L18:L23">
+    <cfRule type="dataBar" priority="6">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -3439,8 +3583,8 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C11">
-    <cfRule type="dataBar" priority="2">
+  <conditionalFormatting sqref="C2:C12">
+    <cfRule type="dataBar" priority="5">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -3453,7 +3597,49 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N7">
+  <conditionalFormatting sqref="M18:M23">
+    <cfRule type="dataBar" priority="4">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{65DAA0BF-C649-45B4-9F37-155E15797282}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C13">
+    <cfRule type="dataBar" priority="3">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{22CB0EF5-EC5D-4714-BF5C-66112D29FEDE}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:C14">
+    <cfRule type="dataBar" priority="2">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{76BBC023-12CB-4669-AF19-E927870BC06D}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L18:M23">
     <cfRule type="dataBar" priority="1">
       <dataBar>
         <cfvo type="min"/>
@@ -3462,7 +3648,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{65DAA0BF-C649-45B4-9F37-155E15797282}</x14:id>
+          <x14:id>{462A7426-4173-46BF-9395-E0F2FEAD1F2F}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -3486,7 +3672,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>M2:M7</xm:sqref>
+          <xm:sqref>L18:L23</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{79DF8A7F-9B9C-44D8-859A-D17098617AEF}">
@@ -3497,7 +3683,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>C2:C11</xm:sqref>
+          <xm:sqref>C2:C12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{65DAA0BF-C649-45B4-9F37-155E15797282}">
@@ -3508,7 +3694,40 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>N2:N7</xm:sqref>
+          <xm:sqref>M18:M23</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{22CB0EF5-EC5D-4714-BF5C-66112D29FEDE}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>C13</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{76BBC023-12CB-4669-AF19-E927870BC06D}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>C2:C14</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{462A7426-4173-46BF-9395-E0F2FEAD1F2F}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>L18:M23</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
